--- a/resi_final.xlsx
+++ b/resi_final.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="99">
   <si>
     <t>Clients</t>
   </si>
@@ -240,6 +240,90 @@
   </si>
   <si>
     <t>ABEILLE BETON  BINGERVILLE</t>
+  </si>
+  <si>
+    <t>AMBASSADE DES ETATS UNIS   RIVIERA GOLF</t>
+  </si>
+  <si>
+    <t>SYTHD190273</t>
+  </si>
+  <si>
+    <t>UNITE DE COORDINATION DES PROJETS SANTE-BANQUE MONDIALE PLA</t>
+  </si>
+  <si>
+    <t>SYTHD240095</t>
+  </si>
+  <si>
+    <t>STE DICK JOEL6   PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD140199</t>
+  </si>
+  <si>
+    <t>TOTAL COTE D'IVOIRE SA   TREICHVILLE</t>
+  </si>
+  <si>
+    <t>SYTHD220249</t>
+  </si>
+  <si>
+    <t>CHAMBRE AGRICULTURE</t>
+  </si>
+  <si>
+    <t>T0</t>
+  </si>
+  <si>
+    <t>ETS AGROSCIENCES</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>ARIANA MAINTENANCE CI SARL UNIPERSONNELLE</t>
+  </si>
+  <si>
+    <t>SOCIETE DE DEVELOPPEMENT DU CAOUTCHOUC IVOIRIEN COCODY DANGA</t>
+  </si>
+  <si>
+    <t>SYTHD150184</t>
+  </si>
+  <si>
+    <t>SYTHD230268</t>
+  </si>
+  <si>
+    <t>SYTHD230262</t>
+  </si>
+  <si>
+    <t>SDA RCI  GROUPE  CFAO PALM CLUB</t>
+  </si>
+  <si>
+    <t>SYTHD210170</t>
+  </si>
+  <si>
+    <t>COPACI   YOPOUGON</t>
+  </si>
+  <si>
+    <t>SYTHD200144</t>
+  </si>
+  <si>
+    <t>SYTHD240203</t>
+  </si>
+  <si>
+    <t>TELENUM COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD230179</t>
+  </si>
+  <si>
+    <t>BRS BROKERS AFRIQUE MARCORY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STE NOUVELLE MICI-EMBACI KOUMASSI ZONE INDUSTRIELLE </t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL DE DEVELOPPEMENT AGIRCOLE VALLON BACK UP</t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL DE DEVELOPPEMENT AGIRCOLE VALLON   PRINCIPAL</t>
   </si>
 </sst>
 </file>
@@ -652,10 +736,10 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61" style="3" customWidth="1"/>
+    <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" style="3" customWidth="1"/>
@@ -1342,7 +1426,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>65</v>
       </c>
@@ -1368,7 +1452,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>65</v>
       </c>
@@ -1394,7 +1478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>65</v>
       </c>
@@ -1420,104 +1504,482 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+    <row r="30" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1835206</v>
+      </c>
       <c r="E30" s="5">
+        <v>901000</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="6">
+        <v>46086</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1835406</v>
+      </c>
+      <c r="E31" s="5">
+        <v>900000</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="6">
+        <v>46086</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1837206</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3571171</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="6">
+        <v>46087</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1837216</v>
+      </c>
+      <c r="E33" s="5">
+        <v>499000</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="6">
+        <v>46087</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="4">
+        <v>2720333000</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1848476</v>
+      </c>
+      <c r="E34" s="5">
+        <v>130000</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="6">
+        <v>46099</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2721215500</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1846056</v>
+      </c>
+      <c r="E35" s="5">
+        <v>254750</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="6">
+        <v>46099</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2721549868</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1850026</v>
+      </c>
+      <c r="E36" s="5">
+        <v>111435</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="6">
+        <v>46104</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1851436</v>
+      </c>
+      <c r="E37" s="5">
+        <v>669565</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="6">
+        <v>46104</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1853236</v>
+      </c>
+      <c r="E38" s="5">
+        <v>570000</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1853246</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1900000</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1853186</v>
+      </c>
+      <c r="E40" s="5">
+        <v>250000</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1853366</v>
+      </c>
+      <c r="E41" s="5">
+        <v>422500</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1853366</v>
+      </c>
+      <c r="E42" s="5">
+        <v>500000</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6">
+        <v>46111</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2721549600</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1853266</v>
+      </c>
+      <c r="E43" s="5">
+        <v>254750</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1853256</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1297512</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5">
         <v>0</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5">
+      <c r="F45" s="4"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5">
         <v>0</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5">
+      <c r="F46" s="4"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5">
         <v>0</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5">
+      <c r="F47" s="4"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5">
         <v>0</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5">
+      <c r="F48" s="4"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5">
         <v>0</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5">
+      <c r="F49" s="4"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5">
         <v>0</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5">
+      <c r="F50" s="4"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5">
         <v>0</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H35"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>

--- a/resi_final.xlsx
+++ b/resi_final.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$29:$H$51</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1979,7 +1979,6 @@
       <c r="H51" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H35"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
